--- a/DATA/production_capacity_scenarios/production_capacity_scenarios_new_20JUN25.xlsx
+++ b/DATA/production_capacity_scenarios/production_capacity_scenarios_new_20JUN25.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/production_capacity_scenarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="111" documentId="8_{660A6D66-C27E-40E3-8B10-8476F2467E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{659A39D7-4C09-4378-AB8D-2EB047B4309E}"/>
+  <xr:revisionPtr revIDLastSave="113" documentId="8_{660A6D66-C27E-40E3-8B10-8476F2467E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CA200CC-E968-4461-BD61-78F9E97FB85C}"/>
   <bookViews>
-    <workbookView xWindow="-21710" yWindow="-15900" windowWidth="21820" windowHeight="37900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-2565" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base_capacity" sheetId="1" r:id="rId1"/>
@@ -175,6 +175,2031 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>base_capacity!$A$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Manufacturer</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>base_capacity!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-90CD-405B-BB01-30E7C062199C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>base_capacity!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>AJ_Vaccines</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>base_capacity!$B$2:$K$2</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>7425522.4005261613</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10186727.531289762</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11907769.057237357</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11862360.77098361</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11841624.98810922</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11668874.186389355</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11882231.998606291</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11698227.981637487</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11906769.550797597</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12102355.415715292</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-90CD-405B-BB01-30E7C062199C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>base_capacity!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>BB_NCIPD</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>base_capacity!$B$3:$K$3</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>52037665.852311946</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>57779574.413046554</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>58193259.25932312</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>55019056.934067987</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>54840408.090443209</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>54476788.035128631</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>54886748.073954158</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>54477550.42504295</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>55217882.849568628</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>55762252.537822999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-90CD-405B-BB01-30E7C062199C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>base_capacity!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Bharat_Biotech</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>base_capacity!$B$4:$K$4</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>76103773.624191374</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>84190111.533407047</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>85660418.668385461</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>82973450.151353627</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>83483087.104019046</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>80741642.426185563</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5399061.594467843</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5342449.0133414418</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5400438.5460411804</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5457031.9499387406</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-90CD-405B-BB01-30E7C062199C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>base_capacity!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Bilthoven</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>base_capacity!$B$5:$K$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>11602101.246511616</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15916381.072431555</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18605444.138496775</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18534495.38820963</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18502096.502399612</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18232179.830701485</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18565543.438748736</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18278044.038775794</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18603882.447037891</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18909478.051597763</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-90CD-405B-BB01-30E7C062199C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>base_capacity!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Biological_E</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>base_capacity!$B$6:$K$6</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>167477790.73029119</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>186369098.6576573</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>188096660.65038288</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>178524775.96577999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>176530850.13874575</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>172990672.99360529</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>675315499.35098982</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>672286110.97072458</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>674655766.38601017</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>676656204.10945988</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-90CD-405B-BB01-30E7C062199C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>base_capacity!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>China_National</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>base_capacity!$B$7:$K$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>13881370.18093955</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15232745.848797543</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15792073.966500476</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16951179.025346309</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17735936.389576431</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>16148650.836001527</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1587996.3137516484</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1592938.8371682856</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1268174.5664170536</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1317354.7756154076</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-90CD-405B-BB01-30E7C062199C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>base_capacity!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>GSK</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>base_capacity!$B$8:$K$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>320888825.67264801</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>337087236.06132972</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>368672725.00520146</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>373752312.13216102</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>396803483.4575721</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>428063809.67389333</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>359240449.77463949</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>392557655.31243134</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>367717286.36545503</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>379834532.08035249</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-90CD-405B-BB01-30E7C062199C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>base_capacity!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Haffkine_Bio</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>base_capacity!$B$9:$K$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>102061729.61303598</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>112436774.10515548</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>114240030.3932219</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>110003002.48402733</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>110309018.17972879</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>106161851.74702463</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-90CD-405B-BB01-30E7C062199C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>base_capacity!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LG_Chem</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>base_capacity!$B$10:$K$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>79331370.747453704</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>90528232.787526816</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>94027137.328041792</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>89461692.512774944</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>89119784.279358327</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>87378488.931086555</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>88457536.048299909</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>87245913.907082528</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>88331646.680949032</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>89157748.448498234</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-90CD-405B-BB01-30E7C062199C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>base_capacity!$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Merck_Sharp</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>base_capacity!$B$11:$K$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>16853370.466626287</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17118470.561035786</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25030720.701507937</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>66404833.399775259</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>84472469.46804361</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>58979732.994024307</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>38500466.743425965</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>38620296.655361526</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>30746489.961206775</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>31938848.527961027</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-90CD-405B-BB01-30E7C062199C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>base_capacity!$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Panacea_Biotec</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>base_capacity!$B$12:$K$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>13954082.083728712</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15632940.469376126</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15891707.329763433</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15172514.527298</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15190636.281435691</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14917453.129769688</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>13822689.963767603</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13695214.864104869</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>13863370.653488748</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14015815.917442642</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-90CD-405B-BB01-30E7C062199C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="12"/>
+          <c:order val="12"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>base_capacity!$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pfizer</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>base_capacity!$B$13:$K$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>90601637.637148559</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>108206253.00727393</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>121034672.59861286</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>119167343.98818734</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>127882016.1090702</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>126787150.39537564</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>128618324.66963975</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>125762346.22839734</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>126589244.00561312</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>127439682.10564198</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-90CD-405B-BB01-30E7C062199C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="13"/>
+          <c:order val="13"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>base_capacity!$A$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PT_Bio</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>base_capacity!$B$14:$K$14</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>62160472.928876854</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>74805768.042486519</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>73129673.71750547</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>66873080.194918983</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>69754435.7609061</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>58660276.607224211</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>43961179.163997561</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>41822903.525532909</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>42390631.016112179</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>42815576.129015923</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000D-90CD-405B-BB01-30E7C062199C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="14"/>
+          <c:order val="14"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>base_capacity!$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sanofi</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>base_capacity!$B$15:$K$15</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>90513261.479781285</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>116530823.28553118</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>131455413.33479622</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>130186693.21709424</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>130099516.09323281</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>127505729.61732844</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>99885732.748712257</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>98345958.901091114</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>100097154.0161474</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>101739447.41935</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000E-90CD-405B-BB01-30E7C062199C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="15"/>
+          <c:order val="15"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>base_capacity!$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Serum_Institute</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>base_capacity!$B$16:$K$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>796886219.83396947</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>818318426.32180607</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>853518482.20633352</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>790797852.0517658</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>816646575.55079889</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>818178645.42941022</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>538741345.62260735</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>619728951.38606513</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>551024467.30856764</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>581266772.68311989</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000F-90CD-405B-BB01-30E7C062199C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1087771055"/>
+        <c:axId val="1087772495"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1087771055"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1087772495"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1087772495"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1087771055"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>57149</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>4761</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>371474</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>180974</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05D3A987-1D4F-00BD-525C-304DADDCA6BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1056,6 +3081,7 @@
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
